--- a/dev/build/encoding-prep/aero-cou1/aero-cou1-extracted.xlsx
+++ b/dev/build/encoding-prep/aero-cou1/aero-cou1-extracted.xlsx
@@ -1386,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1545,14 +1545,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -1605,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1712,7 +1704,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cfx_solver_settings.txt; cou_definition.docx</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1726,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_rig_temperature_data.csv</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1748,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>mesh_convergence_study.csv</t>
         </is>
       </c>
     </row>
@@ -1778,14 +1770,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>cou_definition.docx; cfx_solver_settings.txt; EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+          <t>sensitivity_study_turbulence_intensity.csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -2148,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2233,11 +2221,7 @@
           <t>ValidationResult</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Stable URI or local ID</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="n"/>
       <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Method of Manufactured Solutions benchmarks for conjugate heat transfer coupling covering 1D conduction, 2D convection-diffusion, coupled CHT with rotation, CHT with variable properties, and CHT with turbulence closure.</t>
@@ -2312,7 +2296,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>mesh_convergence_study.csv (primary evidence); credibility_assessment_narrative.docx §1.3 (assessment)</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2343,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_rig_temperature_data.csv (primary evidence); credibility_assessment_narrative.docx §3.2 (assessment)</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2390,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.4</t>
         </is>
       </c>
     </row>
@@ -2448,14 +2432,10 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx; the study CSVs named in EVIDENCE_MANIFEST.txt [CANDIDATE, author confirms at the cell walk]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
+          <t>sensitivity_study_turbulence_intensity.csv (primary evidence); credibility_assessment_narrative.docx §5.5 (assessment)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -2471,7 +2451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2628,7 +2608,7 @@
       <c r="H5" s="10" t="n"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.1</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2647,7 @@
       <c r="H6" s="10" t="n"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.2</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2686,7 @@
       <c r="H7" s="10" t="n"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>mesh_convergence_study.csv (primary evidence); credibility_assessment_narrative.docx §1.3 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2725,7 @@
       <c r="H8" s="10" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cfx_solver_settings.txt (primary evidence); credibility_assessment_narrative.docx §1.4 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2764,7 @@
       <c r="H9" s="10" t="n"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §1.5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2803,7 @@
       <c r="H10" s="10" t="n"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §2.1</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2842,7 @@
       <c r="H11" s="10" t="n"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §2.2</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2881,7 @@
       <c r="H12" s="10" t="n"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_rig_temperature_data.csv (primary evidence); credibility_assessment_narrative.docx §2.3 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2920,7 @@
       <c r="H13" s="10" t="n"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §2.4</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2959,7 @@
       <c r="H14" s="10" t="n"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §3.1</t>
         </is>
       </c>
     </row>
@@ -3018,7 +2998,7 @@
       <c r="H15" s="10" t="n"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>cascade_rig_temperature_data.csv (primary evidence); credibility_assessment_narrative.docx §3.2 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3037,7 @@
       <c r="H16" s="10" t="n"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §4.1</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3056,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
@@ -3085,7 +3065,7 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>The cascade rig used for validation is not film cooled while the engine blade has 47 film cooling holes governing hot-spot temperature; the cascade also does not reproduce annular secondary flows, tip-gap leakage, or rotor-stator unsteadiness, leaving a material applicability gap for the peak-temperature QoI at MRL 3.</t>
+          <t>The cascade rig used for validation is not film cooled while the engine blade has 47 film cooling holes governing hot-spot temperature; the cascade also does not reproduce annular secondary flows, tip-gap leakage, or rotor-stator unsteadiness, leaving a material applicability gap for the peak-temperature QoI at MRL 3. DECLINED MAPPING: the source also states a Film Cooling Validation gap (narrative §4.3, Level 1 achieved against Level 3 required, board-flagged as a material applicability gap). NASA-STD-7009B has no factor for it, so it is not carried as a level here. See AMBIGUITY_LOG G-06.</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -3096,7 +3076,7 @@
       <c r="H17" s="10" t="n"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §4.2; §6 open item 4</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3115,7 @@
       <c r="H18" s="10" t="n"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.1</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3154,7 @@
       <c r="H19" s="10" t="n"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>review_board_minutes_2026Q1.txt (primary evidence); credibility_assessment_narrative.docx §5.2 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3193,7 @@
       <c r="H20" s="10" t="n"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.3</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3230,7 @@
       <c r="H21" s="10" t="n"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.4</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3269,7 @@
       <c r="H22" s="10" t="n"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>sensitivity_study_turbulence_intensity.csv (primary evidence); credibility_assessment_narrative.docx §5.5 (assessed level)</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3308,7 @@
       <c r="H23" s="10" t="n"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>credibility_assessment_narrative.docx [CANDIDATE, author confirms at the cell walk]</t>
+          <t>credibility_assessment_narrative.docx §5.6</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3429,14 +3409,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
